--- a/literature-review/results/results_topic2.xlsx
+++ b/literature-review/results/results_topic2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\177020724\Documents\Studium\Thesis\Literature Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC5FB5E-A16E-4BEE-9CE8-9EB394E70A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1126750C-01FE-4E58-890E-CA6732E75EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-192" yWindow="-192" windowWidth="41664" windowHeight="16944" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="86">
   <si>
     <t>Index</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Serving</t>
-  </si>
-  <si>
-    <t>Deployment</t>
   </si>
   <si>
     <t>Datasource</t>
@@ -156,9 +153,6 @@
     <t>Checkpoints, fully pre-trained models and other artifacts are bundled into a package that is available on GitHub</t>
   </si>
   <si>
-    <t>Only describes certain MLOps tasks, mentions that full MLOps workflows for Active Learning do not exist yet</t>
-  </si>
-  <si>
     <t>Various possible problems mentioned: Image classification and recognition, Object detection and Semantic segmentation</t>
   </si>
   <si>
@@ -193,9 +187,6 @@
   </si>
   <si>
     <t>Mentions post-deployment monitoring</t>
-  </si>
-  <si>
-    <t>Describes LLMs, but also general multi-modal FMs. Stays mostly on surface-level</t>
   </si>
   <si>
     <t>Saturn Platform: Foundation Model Operations and Generative AI for Financial Services</t>
@@ -270,6 +261,27 @@
   </si>
   <si>
     <t>No specific use case, paper describes recent advances in Multi Modal Foundation Models</t>
+  </si>
+  <si>
+    <t>Describes LLMs, but also general multi-modal FMs</t>
+  </si>
+  <si>
+    <t>Only describes subset MLOps tasks, mentions that full MLOps workflows for Active Learning do not exist yet</t>
+  </si>
+  <si>
+    <t>Cloud Deployment</t>
+  </si>
+  <si>
+    <t>Storage of pre-trained models, hyperparameters and benchmarking datasets in a repository</t>
+  </si>
+  <si>
+    <t>Mentions that pipeline tasks should be parallelized and the streamlining of AL processes</t>
+  </si>
+  <si>
+    <t>Mentions pre-processing of biological data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Describes inferencing through a GPU Cloud to ensure scalability and parallelization </t>
   </si>
 </sst>
 </file>
@@ -401,6 +413,19 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -409,6 +434,48 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -424,74 +491,19 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -522,30 +534,30 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0C5B4A38-1107-4982-A90D-0B53B8E3FDD5}" name="Tabelle2" displayName="Tabelle2" ref="A2:X6" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="A2:X6" xr:uid="{0C5B4A38-1107-4982-A90D-0B53B8E3FDD5}"/>
   <tableColumns count="24">
-    <tableColumn id="1" xr3:uid="{D5837C41-A614-42A8-BD06-86F64680F0A2}" name="Index" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{81AE2D55-46F0-4224-8FAC-7F8CBAFBCD93}" name="Title" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{B374F111-5398-4F5C-9065-0C92E010DC0D}" name="Link" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{48D5B335-FEC3-45A1-B599-B37ADA8AB433}" name="Year" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{D517BB4A-F8D9-4A1A-8DAC-4ED55F73B7C5}" name="Use Cases" dataDxfId="3"/>
-    <tableColumn id="26" xr3:uid="{AE43902B-3019-413E-9DBE-7D4A1B1DBDAF}" name="Downstream tasks" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{61F9C5F7-950A-4F76-8C1A-F082BD1F88C8}" name="Type of problem(s) described" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{232E9CE2-4916-4233-BC07-E3E4A3A081B3}" name="Serving" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{5AA90D9C-1033-4A82-BC03-B93164FCC4C1}" name="(Pre-)processing" dataDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{20BC529F-0800-446A-8F47-AC38727C0449}" name="Deployment" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{420767DF-8F51-47D1-A265-155E164F3FB4}" name="Datasource" dataDxfId="19"/>
-    <tableColumn id="27" xr3:uid="{7D4B2930-244D-4367-82DF-567DD2F417C5}" name="Pre-training" dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{EA8AFE10-39EB-4529-8923-318C529A0A0C}" name="Fine-tuning" dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{6A527EF1-5F9E-4EDF-B4A8-E7F94C1E1582}" name="Prediction/Inference" dataDxfId="16"/>
-    <tableColumn id="16" xr3:uid="{22499623-8F36-4FA8-BDEA-B296E884F24D}" name="Reporting" dataDxfId="15"/>
-    <tableColumn id="17" xr3:uid="{777C05CE-3755-41E8-A9E6-0106D49CE8E2}" name="Testing" dataDxfId="14"/>
-    <tableColumn id="18" xr3:uid="{5B8F627A-D638-4FD2-8483-F07CAF8FE05F}" name="Monitoring/Logging" dataDxfId="13"/>
-    <tableColumn id="19" xr3:uid="{A4DB0720-696B-4C80-B5F9-6B8A9D0AD6BC}" name="Annotation" dataDxfId="12"/>
-    <tableColumn id="20" xr3:uid="{A780FEDF-8BD6-4938-A880-AE9AC269950C}" name="Orchestration" dataDxfId="11"/>
-    <tableColumn id="21" xr3:uid="{DFB367C2-30A8-4FC6-9DC2-40E56CC20014}" name="Containerization" dataDxfId="10"/>
-    <tableColumn id="22" xr3:uid="{B359A883-182A-4DE6-9DC6-5D464A89F2C8}" name="Artifact storage" dataDxfId="9"/>
-    <tableColumn id="23" xr3:uid="{36CE1FC6-663C-453D-BB8F-BFFB35C1B9AE}" name="Versioning" dataDxfId="8"/>
-    <tableColumn id="24" xr3:uid="{60046165-6E18-4820-AFF6-3DD2B3F66667}" name="Is a diagram used? What kind?" dataDxfId="0"/>
-    <tableColumn id="25" xr3:uid="{069685CD-673B-446C-9D2F-65DA253E8F53}" name="Comments" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{D5837C41-A614-42A8-BD06-86F64680F0A2}" name="Index" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{81AE2D55-46F0-4224-8FAC-7F8CBAFBCD93}" name="Title" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{B374F111-5398-4F5C-9065-0C92E010DC0D}" name="Link" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{48D5B335-FEC3-45A1-B599-B37ADA8AB433}" name="Year" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{D517BB4A-F8D9-4A1A-8DAC-4ED55F73B7C5}" name="Use Cases" dataDxfId="19"/>
+    <tableColumn id="26" xr3:uid="{AE43902B-3019-413E-9DBE-7D4A1B1DBDAF}" name="Downstream tasks" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{61F9C5F7-950A-4F76-8C1A-F082BD1F88C8}" name="Type of problem(s) described" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{232E9CE2-4916-4233-BC07-E3E4A3A081B3}" name="Serving" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{5AA90D9C-1033-4A82-BC03-B93164FCC4C1}" name="(Pre-)processing" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{20BC529F-0800-446A-8F47-AC38727C0449}" name="Cloud Deployment" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{420767DF-8F51-47D1-A265-155E164F3FB4}" name="Datasource" dataDxfId="13"/>
+    <tableColumn id="27" xr3:uid="{7D4B2930-244D-4367-82DF-567DD2F417C5}" name="Pre-training" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{EA8AFE10-39EB-4529-8923-318C529A0A0C}" name="Fine-tuning" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{6A527EF1-5F9E-4EDF-B4A8-E7F94C1E1582}" name="Prediction/Inference" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{22499623-8F36-4FA8-BDEA-B296E884F24D}" name="Reporting" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{777C05CE-3755-41E8-A9E6-0106D49CE8E2}" name="Testing" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{5B8F627A-D638-4FD2-8483-F07CAF8FE05F}" name="Monitoring/Logging" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{A4DB0720-696B-4C80-B5F9-6B8A9D0AD6BC}" name="Annotation" dataDxfId="6"/>
+    <tableColumn id="20" xr3:uid="{A780FEDF-8BD6-4938-A880-AE9AC269950C}" name="Orchestration" dataDxfId="5"/>
+    <tableColumn id="21" xr3:uid="{DFB367C2-30A8-4FC6-9DC2-40E56CC20014}" name="Containerization" dataDxfId="4"/>
+    <tableColumn id="22" xr3:uid="{B359A883-182A-4DE6-9DC6-5D464A89F2C8}" name="Artifact storage" dataDxfId="3"/>
+    <tableColumn id="23" xr3:uid="{36CE1FC6-663C-453D-BB8F-BFFB35C1B9AE}" name="Versioning" dataDxfId="2"/>
+    <tableColumn id="24" xr3:uid="{60046165-6E18-4820-AFF6-3DD2B3F66667}" name="Is a diagram used? What kind?" dataDxfId="1"/>
+    <tableColumn id="25" xr3:uid="{069685CD-673B-446C-9D2F-65DA253E8F53}" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -839,41 +851,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="31.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="31.1015625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="4" max="4" width="6.5546875" customWidth="1"/>
-    <col min="5" max="6" width="29.109375" customWidth="1"/>
-    <col min="7" max="7" width="28.5546875" customWidth="1"/>
-    <col min="8" max="11" width="20.5546875" customWidth="1"/>
-    <col min="12" max="12" width="35.6640625" customWidth="1"/>
-    <col min="13" max="22" width="20.5546875" customWidth="1"/>
-    <col min="23" max="23" width="36.77734375" customWidth="1"/>
+    <col min="3" max="3" width="23.3125" customWidth="1"/>
+    <col min="4" max="4" width="6.5234375" customWidth="1"/>
+    <col min="5" max="6" width="29.1015625" customWidth="1"/>
+    <col min="7" max="7" width="28.5234375" customWidth="1"/>
+    <col min="8" max="11" width="20.5234375" customWidth="1"/>
+    <col min="12" max="12" width="35.68359375" customWidth="1"/>
+    <col min="13" max="22" width="20.5234375" customWidth="1"/>
+    <col min="23" max="23" width="36.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" ht="18.3" x14ac:dyDescent="0.7">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F1" s="4"/>
       <c r="H1" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="W1" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X1" s="6"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -884,13 +896,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>3</v>
@@ -899,348 +911,348 @@
         <v>4</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="W2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="3" spans="1:24" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="10">
         <v>2024</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="T3" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W3" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="S3" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="T3" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="U3" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>34</v>
-      </c>
     </row>
-    <row r="4" spans="1:24" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="10">
         <v>2023</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="P4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="U4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="V4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="W4" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="X4" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="P4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="T4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="U4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="V4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="W4" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>44</v>
-      </c>
     </row>
-    <row r="5" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="10">
         <v>2023</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="S5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="T5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="U5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="V5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="W5" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="X5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="O5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="R5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="S5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="T5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="U5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="V5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="W5" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>57</v>
-      </c>
     </row>
-    <row r="6" spans="1:24" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" s="7" customFormat="1" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D6" s="10">
         <v>2023</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="N6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W6" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="N6" s="2" t="s">
+      <c r="X6" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W6" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="X6" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
